--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">show_weighted_base</t>
   </si>
   <si>
-    <t xml:space="preserve">Show the weighted base row (the % denominator). Turn off for simpler client tables — the unweighted count and effective base still show.</t>
+    <t xml:space="preserve">Show the weighted base row (the % denominator). Turn off for simpler client tables. The unweighted count and effective base still show.</t>
   </si>
   <si>
     <t xml:space="preserve">weight_label</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">chart_series_colour_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom colour for 1st banner series in bar charts (e.g., Total). Leave blank to auto-generate. You can define some colours and leave others blank — blanks are auto-filled with distinct hues.</t>
+    <t xml:space="preserve">Custom colour for 1st banner series in bar charts (e.g., Total). Leave blank to auto-generate. You can define some colours and leave others blank. Blanks are auto-filled with distinct hues.</t>
   </si>
   <si>
     <t xml:space="preserve">Hex colour code (e.g. #1B365D)</t>
@@ -698,13 +698,46 @@
     <t xml:space="preserve">html_report_v2_microdata</t>
   </si>
   <si>
-    <t xml:space="preserve">Embed the anonymised per-respondent microdata island in the v2 report (coded answer indices + weights — no names, IDs or text). TRUE powers the live filter, custom banners and COMPUTED views. Set FALSE for a confidentiality ship to insider populations (e.g. a small staff survey sent to the employer): the file then carries published aggregates only, and the live features + the Tracking tab switch off for that build. FALSE is REQUIRED wherever min_reporting_base is a promise - with the island present, sub-k detail is reconstructable from the page source. Tip: keep TRUE for your own working copy and build the client copy with FALSE from a second config.</t>
+    <t xml:space="preserve">Embed the anonymised per-respondent microdata island in the v2 report (coded answer indices + weights, no names, IDs or text). TRUE powers the live filter, custom banners and COMPUTED views. Set FALSE for a confidentiality ship to insider populations (e.g. a small staff survey sent to the employer): the file then carries published aggregates only, and the live features switch off for that build. The Tracking tab still works (its current wave is built from the published figures), but no *_wave.json is written - keep the one from your microdata run. FALSE is REQUIRED wherever min_reporting_base is a promise - with the island present, sub-k detail is reconstructable from the page source. Tip: keep TRUE for your own working copy and build the client copy with FALSE from a second config.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_report_v2_interactivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">records</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What powers the v2 report's LIVE views. 'records' embeds the de-identified per-respondent island, coded answer indices and weights: every feature works. 'cube' embeds precomputed group statistics instead: the live filter, custom and composite banners, Differences, Pattern Recognition, confidence detail and the Reader all still work, on the DECLARED variables only, and the file carries no respondent-level records at all. 'none' is published tables with no live views, which is what html_report_v2_microdata = FALSE has always meant. 'cube' REQUIRES min_reporting_base above 1: it withholds any cut in which a group falls below it. Leave blank to inherit from html_report_v2_microdata; setting both and disagreeing is refused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">records, cube or none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_report_v2_filter_vars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra questions a 'cube' build may be filtered and cross-tabbed by, beyond the banner groups, comma separated (e.g. Q008,Q012). Each must be a SINGLE-RESPONSE question with category rows: a multi-mention answer is a set rather than a partition and is not supported in this version. Declare what you know the client will want to cut by. A cut by anything undeclared is refused on the page, which is the point: the client cannot invent a cut the report was not built to answer. Ignored on 'records' and 'none' builds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated question codes, or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_report_v2_cube_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many declared variables a live filter on a 'cube' build may combine. One filter plus a banner is TWO, so 2 is what 'filter and still see every banner' costs, and it is the default. 3 allows a filter on two variables while still showing a banner, at roughly a third more file size and more withheld cuts on a small sample. 1 is filter-or-banner, not both. Ignored on 'records' and 'none' builds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2 or 3</t>
   </si>
   <si>
     <t xml:space="preserve">sampling_note</t>
   </si>
   <si>
-    <t xml:space="preserve">Fieldwork caveat appended to the 'How sure can I be of these numbers?' design sentence in the v2 report — the honest asterisk where fieldwork deviated from the textbook design (e.g. substitution when a selected store was unavailable, replaced clusters, low response). Plain text, one or two sentences. Blank = no note.</t>
+    <t xml:space="preserve">Fieldwork caveat appended to the 'How sure can I be of these numbers?' design sentence in the v2 report. The honest asterisk where fieldwork deviated from the textbook design (e.g. substitution when a selected store was unavailable, replaced clusters, low response). Plain text, one or two sentences. Blank = no note.</t>
   </si>
   <si>
     <t xml:space="preserve">Free text, or leave blank</t>
@@ -716,7 +749,7 @@
     <t xml:space="preserve">Not_Specified</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample design — drives honest confidence vocabulary in the v2 report (probability designs speak confidence intervals / margin of error; otherwise stability intervals / point estimates).</t>
+    <t xml:space="preserve">Sample design. Drives honest confidence vocabulary in the v2 report (probability designs speak confidence intervals / margin of error; otherwise stability intervals / point estimates).</t>
   </si>
   <si>
     <t xml:space="preserve">Not_Specified, Random, Stratified, Cluster, Census, Quota, Online_Panel, Convenience</t>
@@ -746,7 +779,7 @@
     <t xml:space="preserve">html_report_v2_cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Open SAVED copies of the v2 report on a cover page: report title, the Comments sheet's executive summary and background, and the first five Story pins as leading findings. Only affects copies made with Save copy, and only when there is story content to show. FALSE (the default) = saved copies open on the dashboard, as before.</t>
+    <t xml:space="preserve">Open SAVED copies of the v2 report on a cover page: report title, the executive summary (the first narrative screen whose heading starts "Executive summary", else the first screen), and the first five Story pins as leading findings. Only affects copies made with Save copy, and only when there is story content to show. FALSE (the default) = saved copies open on the dashboard, as before.</t>
   </si>
   <si>
     <t xml:space="preserve">html_report_v2_cover_findings</t>
@@ -758,6 +791,15 @@
     <t xml:space="preserve">Whole number of 1 or more, ALL, or leave blank for 5</t>
   </si>
   <si>
+    <t xml:space="preserve">narrative_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Word document (.docx) holding the report's Background and Executive summary. Each Heading 1 starts a screen, with Heading 2, paragraphs, bold and italic, lists, Quote style, pictures and simple tables inside it. Anything else in the document is skipped and named in the console. The path is relative to this config file. Each screen shows on the Report tab and can be pinned to the Story. Blank = the Comments sheet's _BACKGROUND and _EXECUTIVE_SUMMARY cells are used, as before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a .docx file, or leave blank</t>
+  </si>
+  <si>
     <t xml:space="preserve">waves_source</t>
   </si>
   <si>
@@ -785,6 +827,39 @@
     <t xml:space="preserve">File path, or leave blank to auto-detect</t>
   </si>
   <si>
+    <t xml:space="preserve">conjoint_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a conjoint study's contribution file for this project ({output}_cj_island.json, written by the conjoint module). Names it and the report gains a Conjoint tab showing attribute importance, part-worth utilities, model fit and WTP. Blank -&gt; no Conjoint tab, and nothing else about the report changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File path, or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxdiff_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a MaxDiff study's contribution file for this project ({output}_md_island.json, written by the maxdiff module). Names it and the report gains a MaxDiff tab showing item scores, preference shares, TURF and must-haves, with the estimator named. Blank -&gt; no MaxDiff tab, and nothing else changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pricing_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a pricing study's contribution file for this project ({output}_pr_island.json, written by the pricing module). Names it and the report gains a Pricing tab showing the Van Westendorp price points with their intervals, the Gabor-Granger demand and revenue curves, the monadic cells and the recommended price. Blank -&gt; no Pricing tab, and nothing else changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keydriver_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a key driver study's contribution file for this project ({output}_kd_island.json, written by the keydriver module). Names it and the report gains a Key drivers tab showing importance per driver by method with bootstrap intervals, the importance-performance quadrant, the driver by segment matrix with its bases, and the model diagnostics. Blank -&gt; no Key drivers tab, and nothing else changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catdriver_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a categorical driver study's contribution file for this project ({output}_cd_island.json, written by the catdriver module when its v2_island setting is on). Names it and the report gains a Categorical drivers tab showing driver importance, the odds ratio for every driver level with its interval, probability lifts for a named outcome level, the raw factor patterns, any subgroup comparison, and the model diagnostics. Blank -&gt; no Categorical drivers tab, and nothing else changes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAB VISIBILITY (V2 REPORT)</t>
   </si>
   <si>
@@ -809,7 +884,7 @@
     <t xml:space="preserve">show_tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">Show the Tracking tab in the v2 report. It also needs html_report_v2_tracking = TRUE and at least one prior wave in waves_source — without those the tab is absent whatever this is set to.</t>
+    <t xml:space="preserve">Show the Tracking tab in the v2 report. It also needs html_report_v2_tracking = TRUE and at least one prior wave in waves_source, without those the tab is absent whatever this is set to.</t>
   </si>
   <si>
     <t xml:space="preserve">show_qualitative</t>
@@ -818,6 +893,12 @@
     <t xml:space="preserve">Show the Qualitative (comment) tab in the v2 report. It also needs a qual_workbook that joins to the survey.</t>
   </si>
   <si>
+    <t xml:space="preserve">show_save_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Save copy button in the v2 report header. Set FALSE for a copy that is published rather than worked in, such as a public demo or a client copy that must stay the one version of record.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GROUP OVERVIEW TAB (OPTIONAL)</t>
   </si>
   <si>
@@ -833,7 +914,7 @@
     <t xml:space="preserve">patterns_exclude_banners</t>
   </si>
   <si>
-    <t xml:space="preserve">Banners the Group overview tab must skip, comma-separated (label or code, e.g. Interviewer). Operational cuts are fieldwork QC, not client story — without this the tab's lead portrait can be an interviewer effect. The banner still works everywhere else (crosstabs, Differences); it just never becomes a portrait. Blank = scan every banner.</t>
+    <t xml:space="preserve">Banners the Group overview tab must skip, comma-separated (label or code, e.g. Interviewer). Operational cuts are fieldwork QC, not client story, without this the tab's lead portrait can be an interviewer effect. The banner still works everywhere else (crosstabs, Differences); it just never becomes a portrait. Blank = scan every banner.</t>
   </si>
   <si>
     <t xml:space="preserve">Comma-separated banner labels/codes, or leave blank</t>
@@ -845,9 +926,6 @@
     <t xml:space="preserve">Pin the Group overview apex KPI tiles to these question codes, in order (e.g. Q78, Q79). Blank = auto-detect from question titles, which on a study with many section ratings can pick the wrong ones and crowd out the true headline.</t>
   </si>
   <si>
-    <t xml:space="preserve">Comma-separated question codes, or leave blank</t>
-  </si>
-  <si>
     <t xml:space="preserve">insight_exclude_categories</t>
   </si>
   <si>
@@ -863,13 +941,13 @@
     <t xml:space="preserve">generate_reader_report</t>
   </si>
   <si>
-    <t xml:space="preserve">Also build the narrative Reader report (a *_Reader.html file) — a plain-language summary that sits beside the crosstab and deep-links into its tables. Requires html_report_v2 = TRUE (it reuses that report's data layer, so no statistic is recomputed). Deterministic and on-device by default: no data leaves this machine.</t>
+    <t xml:space="preserve">Also build the narrative Reader report (a *_Reader.html file): a plain-language summary that sits beside the crosstab and deep-links into its tables. Requires html_report_v2 = TRUE (it reuses that report's data layer, so no statistic is recomputed). Deterministic and on-device by default: no data leaves this machine.</t>
   </si>
   <si>
     <t xml:space="preserve">reader_ai_prose</t>
   </si>
   <si>
-    <t xml:space="preserve">Draft the Reader narrative with an AI model instead of the built-in template (only used when generate_reader_report = TRUE). Requires an Anthropic API key in the ANTHROPIC_API_KEY environment variable. Only aggregate figures are sent — never microdata or verbatims — and every number the model writes is checked against the data. If the model is unavailable the report falls back to the on-device narrative and says so.</t>
+    <t xml:space="preserve">Draft the Reader narrative with an AI model instead of the built-in template (only used when generate_reader_report = TRUE). Requires an Anthropic API key in the ANTHROPIC_API_KEY environment variable. Only aggregate figures are sent, never microdata or verbatims, and every number the model writes is checked against the data. If the model is unavailable the report falls back to the on-device narrative and says so.</t>
   </si>
   <si>
     <t xml:space="preserve">ANALYST &amp; CLOSING SECTION</t>
@@ -950,7 +1028,7 @@
     <t xml:space="preserve">project_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+    <t xml:space="preserve">Project name. Appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
   </si>
   <si>
     <t xml:space="preserve">Free text</t>
@@ -959,7 +1037,7 @@
     <t xml:space="preserve">research_house</t>
   </si>
   <si>
-    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+    <t xml:space="preserve">Research organisation name. Appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
   </si>
   <si>
     <t xml:space="preserve">QUALITATIVE (COMMENT) TAB (OPTIONAL)</t>
@@ -968,7 +1046,7 @@
     <t xml:space="preserve">qual_workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Path to the coded-comment workbook (the Comment Appendix), relative to THIS config file — include the subfolder or it will not be found. Set it to switch on the Qualitative tab; leave blank for no comment tab.</t>
+    <t xml:space="preserve">Path to the coded-comment workbook (the Comment Appendix), relative to THIS config file. Include the subfolder or it will not be found. Set it to switch on the Qualitative tab; leave blank for no comment tab.</t>
   </si>
   <si>
     <t xml:space="preserve">e.g. 02 Data/&lt;project&gt; Comment Appendix.xlsx</t>
@@ -980,7 +1058,7 @@
     <t xml:space="preserve">hidden</t>
   </si>
   <si>
-    <t xml:space="preserve">How verbatim text is shown: 'hidden' = numbers only (the safe default — shows NO text); 'redacted' = auto-scrub names / emails / phone numbers; 'full' = as typed. Use 'redacted' or 'full' to display the comments.</t>
+    <t xml:space="preserve">How verbatim text is shown: 'hidden' = numbers only (the safe default, shows NO text); 'redacted' = auto-scrub names / emails / phone numbers; 'full' = as typed. Use 'redacted' or 'full' to display the comments.</t>
   </si>
   <si>
     <t xml:space="preserve">hidden, redacted, or full</t>
@@ -1004,7 +1082,7 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">Which noteworthy tier the comment filter opens on: 'all', 'noteworthy' (tier 1+), 'must_read' (tier 2+), or 'priority' (tier 3 — the lead-with comments).</t>
+    <t xml:space="preserve">Which noteworthy tier the comment filter opens on: 'all', 'noteworthy' (tier 1+), 'must_read' (tier 2+), or 'priority' (tier 3, the lead-with comments).</t>
   </si>
   <si>
     <t xml:space="preserve">all, noteworthy, must_read, or priority</t>
@@ -1013,7 +1091,7 @@
     <t xml:space="preserve">qual_verbatim_scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Which comments ship their readable text (a BUILD-TIME curation, not a reader filter): 'all' = every comment except those marked 'hide'/'hidden' in the noteworthy column; 'noteworthy' = only tier 1+ comments (noteworthy / must-read / priority). Withheld comments are still counted in the theme distribution and base sizes — only their verbatim text is withheld from the file, so a curated handful of quotes ships while the numbers reflect every comment. Theme all, show some.</t>
+    <t xml:space="preserve">Which comments ship their readable text (a BUILD-TIME curation, not a reader filter): 'all' = every comment except those marked 'hide'/'hidden' in the noteworthy column; 'noteworthy' = only tier 1+ comments (noteworthy / must-read / priority). Withheld comments are still counted in the theme distribution and base sizes, only their verbatim text is withheld from the file, so a curated handful of quotes ships while the numbers reflect every comment. Theme all, show some.</t>
   </si>
   <si>
     <t xml:space="preserve">all or noteworthy</t>
@@ -1022,7 +1100,7 @@
     <t xml:space="preserve">qual_tag_dimensions</t>
   </si>
   <si>
-    <t xml:space="preserve">Host-survey columns shown as comment tags, reached via the ResponseID join — a comma list of 'Column' or 'Column:Label', e.g. 'S01:Centre, S09:Channel'. Values are shown as their Survey_Structure DisplayText, so a coded column tags readably. The Label is only what the chip says — check it against the Questions sheet, or the chip will confidently mis-name the column. Governed by qual_demographic_cuts + min_reporting_base. Blank = only the workbook's own demographic columns are tagged.</t>
+    <t xml:space="preserve">Host-survey columns shown as comment tags, reached via the ResponseID join. A comma list of 'Column' or 'Column:Label', e.g. 'S01:Centre, S09:Channel'. Values are shown as their Survey_Structure DisplayText, so a coded column tags readably. The Label is only what the chip says. Check it against the Questions sheet, or the chip will confidently mis-name the column. Governed by qual_demographic_cuts + min_reporting_base. Blank = only the workbook's own demographic columns are tagged.</t>
   </si>
   <si>
     <t xml:space="preserve">e.g. S01:Centre, S09:Channel</t>
@@ -1148,7 +1226,7 @@
     <t xml:space="preserve">[Optional] Human-readable label shown in reports instead of the filter expression. Leave blank to show the raw filter.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Open-ends only: the comment-workbook sheet(s) holding this question's comments. One sheet for a normal open-end. For a 'why?' split across several sheets (e.g. an NPS follow-up), list them as 'Sheet:Band; Sheet:Band' to reassemble into ONE question with a band you can view by — e.g. 'DetractorComment:Detractor; PassiveComment:Passive; PromoterComment:Promoter'. Leave blank for closed questions.</t>
+    <t xml:space="preserve">[Optional] Open-ends only: the comment-workbook sheet(s) holding this question's comments. One sheet for a normal open-end. For a 'why?' split across several sheets (e.g. an NPS follow-up), list them as 'Sheet:Band; Sheet:Band' to reassemble into ONE question with a band you can view by, e.g. 'DetractorComment:Detractor; PassiveComment:Passive; PromoterComment:Promoter'. Leave blank for closed questions.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Diagnostic open-ends only: the closed question or composite this open-end explains (e.g. Q_Engage), which enables jump-to-comments. Leave blank for a generic/standalone open-end.</t>
@@ -1313,7 +1391,7 @@
     <t xml:space="preserve">Headline</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY / _REPORT_CONSTRUCTION for report sections.</t>
+    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY / _REPORT_CONSTRUCTION for report sections. A QUAL_ code targets the Qualitative tab instead of the crosstab card: QUAL_ plus the coded-comment worksheet name, uppercased, non-alphanumerics as underscores (sheet 'Q02Comment' -&gt; QUAL_Q02COMMENT). The Qualitative page prints the exact code in its empty insight box. Banner is ignored on a QUAL_ row.</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Comment text. Supports markdown for HTML reports (bold, bullets, links).</t>
@@ -1347,6 +1425,12 @@
   </si>
   <si>
     <t xml:space="preserve">Satisfaction is up 5 points, driven by service quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUAL_Q_COMMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall, the comments are dominated by delivery reliability.</t>
   </si>
   <si>
     <t xml:space="preserve">Report Text Overrides (optional)</t>
@@ -3402,24 +3486,24 @@
         <v>227</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="C95" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>231</v>
+        <v>35</v>
       </c>
       <c r="C96" s="16" t="s">
         <v>4</v>
@@ -3436,21 +3520,21 @@
         <v>234</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C97" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>35</v>
@@ -3459,49 +3543,49 @@
         <v>4</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
       <c r="C99" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>33</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>35</v>
@@ -3510,49 +3594,49 @@
         <v>4</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C102" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>35</v>
@@ -3561,118 +3645,134 @@
         <v>4</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
+      <c r="A105" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>33</v>
+        <v>262</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>33</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C108" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>33</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C109" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C110" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
+      <c r="A111" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E111" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>35</v>
@@ -3681,15 +3781,15 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>35</v>
@@ -3698,67 +3798,67 @@
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E113" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E113" s="14" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="114">
-      <c r="A114" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C114" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>275</v>
-      </c>
+      <c r="A114" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>278</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
+      <c r="A116" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C117" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E117" s="14" t="s">
         <v>33</v>
@@ -3766,67 +3866,67 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
+      <c r="A119" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C120" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="B121" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C121" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="E121" s="14" t="s">
-        <v>289</v>
-      </c>
+      <c r="A121" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
     </row>
     <row r="122">
       <c r="A122" s="15" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>35</v>
@@ -3835,15 +3935,15 @@
         <v>4</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="15" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>35</v>
@@ -3852,15 +3952,15 @@
         <v>4</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>216</v>
+        <v>299</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>35</v>
@@ -3869,32 +3969,32 @@
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>297</v>
+        <v>233</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -3903,7 +4003,7 @@
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>31</v>
@@ -3912,7 +4012,7 @@
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E127" s="14" t="s">
         <v>33</v>
@@ -3920,24 +4020,24 @@
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>305</v>
+        <v>31</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -3946,7 +4046,7 @@
     </row>
     <row r="130">
       <c r="A130" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>35</v>
@@ -3955,15 +4055,15 @@
         <v>4</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>311</v>
+        <v>208</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>35</v>
@@ -3972,24 +4072,32 @@
         <v>4</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
+      <c r="A132" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="15" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>35</v>
@@ -3998,112 +4106,258 @@
         <v>4</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="C134" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>323</v>
+        <v>127</v>
       </c>
       <c r="C135" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="B136" s="11" t="s">
+      <c r="A136" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C136" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>329</v>
-      </c>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="9"/>
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>327</v>
+        <v>31</v>
       </c>
       <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>332</v>
+        <v>33</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E138" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="B138" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D138" s="13" t="s">
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="E138" s="14" t="s">
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
+      <c r="E139" s="9"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="s">
+      <c r="B140" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D140" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="B139" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D139" s="13" t="s">
+      <c r="E140" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="E139" s="14" t="s">
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="s">
         <v>338</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E141" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E143" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E144" s="14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E145" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E146" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E147" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E148" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E149" s="14" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -4124,15 +4378,15 @@
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A92:E92"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A121:E121"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A142:E142"/>
   </mergeCells>
-  <dataValidations count="15">
+  <dataValidations count="16">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B27:B27">
       <formula1>0</formula1>
       <formula2>4</formula2>
@@ -4193,12 +4447,16 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B97:B97">
+      <formula1>1</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="52">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="55">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx"</xm:f>
@@ -4411,13 +4669,19 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
+            <xm:f>"records,cube,none"</xm:f>
           </x14:formula1>
-          <xm:sqref>B96:B96</xm:sqref>
+          <xm:sqref>B95:B95</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"1,2,3"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B97:B97</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
           <xm:sqref>B99:B99</xm:sqref>
         </x14:dataValidation>
@@ -4425,55 +4689,49 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B100:B100</xm:sqref>
+          <xm:sqref>B102:B102</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B106:B106</xm:sqref>
+          <xm:sqref>B103:B103</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B107:B107</xm:sqref>
+          <xm:sqref>B115:B115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B108:B108</xm:sqref>
+          <xm:sqref>B116:B116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B109:B109</xm:sqref>
+          <xm:sqref>B117:B117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B110:B110</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B117:B117</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
-          </x14:formula1>
           <xm:sqref>B118:B118</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B125:B125</xm:sqref>
+          <xm:sqref>B119:B119</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B120:B120</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4483,33 +4741,51 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
+            <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
           <xm:sqref>B128:B128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B135:B135</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"FALSE,TRUE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B137:B137</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B138:B138</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B134:B134</xm:sqref>
+          <xm:sqref>B144:B144</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B135:B135</xm:sqref>
+          <xm:sqref>B145:B145</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B136:B136</xm:sqref>
+          <xm:sqref>B146:B146</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B137:B137</xm:sqref>
+          <xm:sqref>B147:B147</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4546,159 +4822,159 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -4737,18 +5013,18 @@
         <v>35</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -4799,18 +5075,18 @@
         <v>35</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>35</v>
@@ -4822,7 +5098,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>35</v>
@@ -4849,10 +5125,10 @@
         <v>35</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="R7" s="17" t="s">
         <v>35</v>
@@ -4861,18 +5137,18 @@
         <v>35</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
@@ -4884,7 +5160,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -4911,19 +5187,19 @@
         <v>35</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="T8" s="17" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -6094,122 +6370,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -6235,48 +6511,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -6287,10 +6563,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -6301,10 +6577,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
@@ -6315,23 +6591,31 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="A9" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -6506,6 +6790,12 @@
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6528,28 +6818,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5">
@@ -6654,42 +6944,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6697,10 +6987,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6834,56 +7124,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">Question Comments &amp; Report Text</t>
   </si>
   <si>
-    <t xml:space="preserve">Add question-specific comments and report narrative sections. Use _BACKGROUND, _EXECUTIVE_SUMMARY and _REPORT_CONSTRUCTION for report sections.</t>
+    <t xml:space="preserve">Add question-specific comments and report narrative sections. Use _BACKGROUND, _EXECUTIVE_SUMMARY and _REPORT_CONSTRUCTION for report sections. A Word document named in the Settings sheet's narrative_file replaces _BACKGROUND and _EXECUTIVE_SUMMARY.</t>
   </si>
   <si>
     <t xml:space="preserve">Comment</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">Headline</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY / _REPORT_CONSTRUCTION for report sections. A QUAL_ code targets the Qualitative tab instead of the crosstab card: QUAL_ plus the coded-comment worksheet name, uppercased, non-alphanumerics as underscores (sheet 'Q02Comment' -&gt; QUAL_Q02COMMENT). The Qualitative page prints the exact code in its empty insight box. Banner is ignored on a QUAL_ row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Comment text. Supports markdown for HTML reports (bold, bullets, links).</t>
+    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY / _REPORT_CONSTRUCTION for report sections (_BACKGROUND and _EXECUTIVE_SUMMARY are used only when the Settings sheet's narrative_file is blank). A QUAL_ code targets the Qualitative tab instead of the crosstab card: QUAL_ plus the coded-comment worksheet name, uppercased, non-alphanumerics as underscores (sheet 'Q02Comment' -&gt; QUAL_Q02COMMENT). The Qualitative page prints the exact code in its empty insight box. Banner is ignored on a QUAL_ row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Comment text. Supports markdown for HTML reports (bold, bullets, links). In _BACKGROUND and _EXECUTIVE_SUMMARY each line is its own paragraph and a line starting "- " or "* " is a bullet; nothing else is formatted.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Optional: specific banner column this comment applies to. Leave blank for all banners.</t>

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -794,7 +794,7 @@
     <t xml:space="preserve">narrative_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Word document (.docx) holding the report's Background and Executive summary. Each Heading 1 starts a screen, with Heading 2, paragraphs, bold and italic, lists, Quote style, pictures and simple tables inside it. Anything else in the document is skipped and named in the console. The path is relative to this config file. Each screen shows on the Report tab and can be pinned to the Story. Blank = the Comments sheet's _BACKGROUND and _EXECUTIVE_SUMMARY cells are used, as before.</t>
+    <t xml:space="preserve">Word document (.docx) holding the report's Background and Executive summary. Each Heading 1 starts a screen, with Heading 2 and 3, paragraphs, bold, italic, coloured and highlighted words (shown in the report's own colours), lists, Quote style, pictures and simple tables inside it. Anything else in the document is skipped and named in the console. The path is relative to this config file. Each screen shows on the Report tab and can be pinned to the Story. Blank = the Comments sheet's _BACKGROUND and _EXECUTIVE_SUMMARY cells are used, as before.</t>
   </si>
   <si>
     <t xml:space="preserve">Path to a .docx file, or leave blank</t>

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -858,6 +858,12 @@
   </si>
   <si>
     <t xml:space="preserve">Path to a categorical driver study's contribution file for this project ({output}_cd_island.json, written by the catdriver module when its v2_island setting is on). Names it and the report gains a Categorical drivers tab showing driver importance, the odds ratio for every driver level with its interval, probability lifts for a named outcome level, the raw factor patterns, any subgroup comparison, and the model diagnostics. Blank -&gt; no Categorical drivers tab, and nothing else changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whatif_island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to a What if study's contribution file for this project ({output_name}_whatif_island.json, written by the whatif module). Names it and the report gains a What if tab: where to direct effort, scenarios and Build a ... . A full report gets the live version that follows the filter bar; a client-safe report gets precomputed results for published groups only. Blank -&gt; no What if tab, and nothing else changes.</t>
   </si>
   <si>
     <t xml:space="preserve">TAB VISIBILITY (V2 REPORT)</t>
@@ -3805,30 +3811,30 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
+      <c r="B114" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D115" s="13" t="s">
+      <c r="A115" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E115" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
@@ -3916,63 +3922,63 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="s">
+      <c r="A121" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
+      <c r="B121" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="B122" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C122" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D122" s="13" t="s">
+      <c r="A122" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E122" s="14" t="s">
-        <v>296</v>
-      </c>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
     </row>
     <row r="123">
       <c r="A123" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B123" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D123" s="13" t="s">
+      <c r="E123" s="14" t="s">
         <v>298</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="B124" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C124" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D124" s="13" t="s">
+      <c r="E124" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="125">
@@ -3989,34 +3995,34 @@
         <v>303</v>
       </c>
       <c r="E125" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="s">
+      <c r="B126" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D126" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
+      <c r="E126" s="14" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="B127" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C127" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D127" s="13" t="s">
+      <c r="A127" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="E127" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
@@ -4036,30 +4042,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
+      <c r="B129" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="B130" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D130" s="13" t="s">
+      <c r="A130" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="E130" s="14" t="s">
-        <v>208</v>
-      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
@@ -4075,41 +4081,41 @@
         <v>314</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>315</v>
+        <v>208</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="B132" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D132" s="13" t="s">
+      <c r="E132" s="14" t="s">
         <v>317</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D133" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="B133" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D133" s="13" t="s">
+      <c r="E133" s="14" t="s">
         <v>320</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="134">
@@ -4126,238 +4132,255 @@
         <v>322</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>323</v>
+        <v>216</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="E135" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B136" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C135" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="s">
+      <c r="C136" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
+      <c r="E136" s="14" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="B137" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D137" s="13" t="s">
+      <c r="A137" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="E137" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
         <v>330</v>
       </c>
       <c r="B138" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="C138" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D138" s="13" t="s">
+      <c r="E138" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="E138" s="14" t="s">
+      <c r="B139" s="11" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="9" t="s">
+      <c r="C139" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
+      <c r="E139" s="14" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D140" s="13" t="s">
+      <c r="A140" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="E140" s="14" t="s">
-        <v>337</v>
-      </c>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9"/>
+      <c r="E140" s="9"/>
     </row>
     <row r="141">
       <c r="A141" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="B141" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D141" s="13" t="s">
+      <c r="E141" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="E141" s="14" t="s">
-        <v>337</v>
-      </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
+      <c r="B142" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E142" s="14" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C143" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D143" s="13" t="s">
+      <c r="A143" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="E143" s="14" t="s">
-        <v>343</v>
-      </c>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
     </row>
     <row r="144">
       <c r="A144" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D144" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="E144" s="14" t="s">
         <v>345</v>
-      </c>
-      <c r="C144" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="E144" s="14" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D145" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="E145" s="14" t="s">
         <v>349</v>
-      </c>
-      <c r="C145" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="E145" s="14" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="E146" s="14" t="s">
         <v>353</v>
-      </c>
-      <c r="C146" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D147" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B147" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="C147" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D147" s="13" t="s">
+      <c r="E147" s="14" t="s">
         <v>357</v>
-      </c>
-      <c r="E147" s="14" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D148" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="B148" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C148" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D148" s="13" t="s">
+      <c r="E148" s="14" t="s">
         <v>360</v>
-      </c>
-      <c r="E148" s="14" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D149" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="B149" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C149" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D149" s="13" t="s">
+      <c r="E149" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="E149" s="14" t="s">
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="s">
         <v>364</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E150" s="14" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -4378,13 +4401,13 @@
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A92:E92"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A143:E143"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B27:B27">
@@ -4701,12 +4724,6 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B115:B115</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
           <xm:sqref>B116:B116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -4735,9 +4752,9 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B127:B127</xm:sqref>
+          <xm:sqref>B121:B121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4747,45 +4764,51 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"FALSE,TRUE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B129:B129</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B135:B135</xm:sqref>
+          <xm:sqref>B136:B136</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B137:B137</xm:sqref>
+          <xm:sqref>B138:B138</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B138:B138</xm:sqref>
+          <xm:sqref>B139:B139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B144:B144</xm:sqref>
+          <xm:sqref>B145:B145</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B145:B145</xm:sqref>
+          <xm:sqref>B146:B146</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B146:B146</xm:sqref>
+          <xm:sqref>B147:B147</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B147:B147</xm:sqref>
+          <xm:sqref>B148:B148</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4822,159 +4845,159 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -5013,18 +5036,18 @@
         <v>35</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -5075,61 +5098,61 @@
         <v>35</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>411</v>
-      </c>
       <c r="R7" s="17" t="s">
         <v>35</v>
       </c>
@@ -5137,18 +5160,18 @@
         <v>35</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
@@ -5160,7 +5183,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -5187,19 +5210,19 @@
         <v>35</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="R8" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="S8" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="S8" s="17" t="s">
-        <v>416</v>
-      </c>
       <c r="T8" s="17" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -6370,122 +6393,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -6511,48 +6534,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -6563,10 +6586,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -6577,10 +6600,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
@@ -6591,24 +6614,24 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>35</v>
@@ -6818,28 +6841,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5">
@@ -6944,42 +6967,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6987,10 +7010,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -7124,56 +7147,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -833,7 +833,7 @@
     <t xml:space="preserve">Path to a conjoint study's contribution file for this project ({output}_cj_island.json, written by the conjoint module). Names it and the report gains a Conjoint tab showing attribute importance, part-worth utilities, model fit and WTP. Blank -&gt; no Conjoint tab, and nothing else about the report changes.</t>
   </si>
   <si>
-    <t xml:space="preserve">File path, or leave blank</t>
+    <t xml:space="preserve">Path relative to this config file, or a full path, or leave blank</t>
   </si>
   <si>
     <t xml:space="preserve">maxdiff_island</t>
